--- a/automated_test/vulnerability_report.xlsx
+++ b/automated_test/vulnerability_report.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
